--- a/scenarios/sng_area.xlsx
+++ b/scenarios/sng_area.xlsx
@@ -19,27 +19,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="6">
   <si>
     <t>parameter</t>
-  </si>
-  <si>
-    <t>f_land_use</t>
-  </si>
-  <si>
-    <t>max_land_use_factor</t>
-  </si>
-  <si>
-    <t>semi-natural grasslands</t>
   </si>
   <si>
     <t>val_is</t>
   </si>
   <si>
-    <t>rel</t>
+    <t>y_0</t>
   </si>
   <si>
-    <t>y_0</t>
+    <t>f_region</t>
+  </si>
+  <si>
+    <t>x0_crops</t>
+  </si>
+  <si>
+    <t>rel</t>
   </si>
 </sst>
 </file>
@@ -357,40 +354,1517 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
+      <c r="A2">
+        <v>1011</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>1.87597672155844</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>111</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>4.7966697261919498</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>1111</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>1.73253331572869</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>1112</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>1.62447681279139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>112</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>4.1155882571376203</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>1121</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>1.62883398773806</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>1122</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>1.8125491189935801</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>1123</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>3.8208776762799701</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1124</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <v>2.0991277963504298</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>1131</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11">
+        <v>2.2965314142326099</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>1211</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12">
+        <v>2.4260184761486099</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>1212</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <v>2.7511360327033101</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1213</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>2.0043464757295801</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>1214</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <v>3.8016632543626501</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1215</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16">
+        <v>2.1860438652090601</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1216</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17">
+        <v>3.7419408644899002</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1221</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18">
+        <v>2.03671043872678</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1222</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19">
+        <v>3.0002588520210298</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>1311</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20">
+        <v>1.75558613614286</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>1321</v>
+      </c>
+      <c r="B21" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21">
+        <v>3.0687775425790198</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>1322</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22">
+        <v>1.4707367575063699</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>1331</v>
+      </c>
+      <c r="B23" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23">
+        <v>2.7695911023584299</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>1411</v>
+      </c>
+      <c r="B24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24">
+        <v>4.0074835528083099</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>1412</v>
+      </c>
+      <c r="B25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25">
+        <v>5.8848678617193002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>1421</v>
+      </c>
+      <c r="B26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26">
+        <v>3.1573704858815899</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>1511</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27">
+        <v>1.7623616900066801</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>1512</v>
+      </c>
+      <c r="B28" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28">
+        <v>4.2265575310279697</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>1521</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29">
+        <v>3.1926779821404199</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>1522</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30">
+        <v>4.6875698927495097</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>1611</v>
+      </c>
+      <c r="B31" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31">
+        <v>2.2630865252163899</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>1612</v>
+      </c>
+      <c r="B32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C32" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32">
+        <v>1.92483975615819</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>1613</v>
+      </c>
+      <c r="B33" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33">
+        <v>1.79194480793585</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>1614</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34">
+        <v>2.4002526574929202</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>1615</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4</v>
+      </c>
+      <c r="C35" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35">
+        <v>1.9774115412109201</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>1616</v>
+      </c>
+      <c r="B36" t="s">
+        <v>4</v>
+      </c>
+      <c r="C36" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36">
+        <v>2.36740392075078</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>1617</v>
+      </c>
+      <c r="B37" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37">
+        <v>3.4019167042185199</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>1621</v>
+      </c>
+      <c r="B38" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38">
+        <v>3.34762513542044</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>1622</v>
+      </c>
+      <c r="B39" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39">
+        <v>1.8125262857851701</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>1623</v>
+      </c>
+      <c r="B40" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40">
+        <v>1.85562930513462</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>1711</v>
+      </c>
+      <c r="B41" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41">
+        <v>2.8212114843084599</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>1712</v>
+      </c>
+      <c r="B42" t="s">
+        <v>4</v>
+      </c>
+      <c r="C42" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42">
+        <v>4.8422214575536602</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>1713</v>
+      </c>
+      <c r="B43" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43">
+        <v>4.5027059133621004</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>1721</v>
+      </c>
+      <c r="B44" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44">
+        <v>6.9386897317251401</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>1722</v>
+      </c>
+      <c r="B45" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45">
+        <v>4.8034673589599297</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>1723</v>
+      </c>
+      <c r="B46" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46">
+        <v>3.5877283386024801</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>1724</v>
+      </c>
+      <c r="B47" t="s">
+        <v>4</v>
+      </c>
+      <c r="C47" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47">
+        <v>3.66973191569546</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>1811</v>
+      </c>
+      <c r="B48" t="s">
+        <v>4</v>
+      </c>
+      <c r="C48" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48">
+        <v>4.0211156034803102</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>1812</v>
+      </c>
+      <c r="B49" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49">
+        <v>2.9805289501951702</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>1813</v>
+      </c>
+      <c r="B50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50">
+        <v>4.1336746669063302</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>1821</v>
+      </c>
+      <c r="B51" t="s">
+        <v>4</v>
+      </c>
+      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51">
+        <v>3.6126271612956602</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>1911</v>
+      </c>
+      <c r="B52" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52">
+        <v>1.9740300855911499</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>1912</v>
+      </c>
+      <c r="B53" t="s">
+        <v>4</v>
+      </c>
+      <c r="C53" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53">
+        <v>3.1952272674503601</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>1921</v>
+      </c>
+      <c r="B54" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54">
+        <v>3.29415605694988</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>1922</v>
+      </c>
+      <c r="B55" t="s">
+        <v>4</v>
+      </c>
+      <c r="C55" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55">
+        <v>4.1000635640074696</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>2011</v>
+      </c>
+      <c r="B56" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56">
+        <v>3.4750390641475901</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>2012</v>
+      </c>
+      <c r="B57" t="s">
+        <v>4</v>
+      </c>
+      <c r="C57" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57">
+        <v>3.6220030595297099</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>2019</v>
+      </c>
+      <c r="B58" t="s">
+        <v>4</v>
+      </c>
+      <c r="C58" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58">
+        <v>11.6606957415257</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>2111</v>
+      </c>
+      <c r="B59" t="s">
+        <v>4</v>
+      </c>
+      <c r="C59" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59">
+        <v>3.4755008202532101</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>2121</v>
+      </c>
+      <c r="B60" t="s">
+        <v>4</v>
+      </c>
+      <c r="C60" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60">
+        <v>6.6232951283394499</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>2122</v>
+      </c>
+      <c r="B61" t="s">
+        <v>4</v>
+      </c>
+      <c r="C61" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61">
+        <v>6.0641799019937999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>2211</v>
+      </c>
+      <c r="B62" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62">
+        <v>10.440691974867301</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>2212</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63">
+        <v>21.694189136708498</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>2221</v>
+      </c>
+      <c r="B64" t="s">
+        <v>4</v>
+      </c>
+      <c r="C64" t="s">
+        <v>5</v>
+      </c>
+      <c r="D64">
+        <v>14.866676478140199</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>2311</v>
+      </c>
+      <c r="B65" t="s">
+        <v>4</v>
+      </c>
+      <c r="C65" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65">
+        <v>3.04563165921234</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>2312</v>
+      </c>
+      <c r="B66" t="s">
+        <v>4</v>
+      </c>
+      <c r="C66" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66">
+        <v>3.6172231028992701</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>2319</v>
+      </c>
+      <c r="B67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C67" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67">
+        <v>2.3303101882114898</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>2331</v>
+      </c>
+      <c r="B68" t="s">
+        <v>4</v>
+      </c>
+      <c r="C68" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68">
+        <v>2.7907423334474899</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>2411</v>
+      </c>
+      <c r="B69" t="s">
+        <v>4</v>
+      </c>
+      <c r="C69" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69">
+        <v>16.2274542777891</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>2412</v>
+      </c>
+      <c r="B70" t="s">
+        <v>4</v>
+      </c>
+      <c r="C70" t="s">
+        <v>5</v>
+      </c>
+      <c r="D70">
+        <v>17.569232226179199</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>2413</v>
+      </c>
+      <c r="B71" t="s">
+        <v>4</v>
+      </c>
+      <c r="C71" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71">
+        <v>65.477368244887401</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>2414</v>
+      </c>
+      <c r="B72" t="s">
+        <v>4</v>
+      </c>
+      <c r="C72" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72">
+        <v>24.820011081532002</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>2415</v>
+      </c>
+      <c r="B73" t="s">
+        <v>4</v>
+      </c>
+      <c r="C73" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73">
+        <v>28.173516566704802</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>2419</v>
+      </c>
+      <c r="B74" t="s">
+        <v>4</v>
+      </c>
+      <c r="C74" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74">
+        <v>4.2595138480394503</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>2511</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75">
+        <v>39.438363083511703</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>2512</v>
+      </c>
+      <c r="B76" t="s">
+        <v>4</v>
+      </c>
+      <c r="C76" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76">
+        <v>15.415977648064199</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>2519</v>
+      </c>
+      <c r="B77" t="s">
+        <v>4</v>
+      </c>
+      <c r="C77" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77">
+        <v>34.314893531409197</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>2521</v>
+      </c>
+      <c r="B78" t="s">
+        <v>4</v>
+      </c>
+      <c r="C78" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78">
+        <v>13.7644740502676</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>311</v>
+      </c>
+      <c r="B79" t="s">
+        <v>4</v>
+      </c>
+      <c r="C79" t="s">
+        <v>5</v>
+      </c>
+      <c r="D79">
+        <v>3.0801374032695499</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>312</v>
+      </c>
+      <c r="B80" t="s">
+        <v>4</v>
+      </c>
+      <c r="C80" t="s">
+        <v>5</v>
+      </c>
+      <c r="D80">
+        <v>2.7719312933184499</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>321</v>
+      </c>
+      <c r="B81" t="s">
+        <v>4</v>
+      </c>
+      <c r="C81" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81">
+        <v>3.0091344153636399</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>322</v>
+      </c>
+      <c r="B82" t="s">
+        <v>4</v>
+      </c>
+      <c r="C82" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82">
+        <v>2.6590329047539498</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>411</v>
+      </c>
+      <c r="B83" t="s">
+        <v>4</v>
+      </c>
+      <c r="C83" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83">
+        <v>2.1698208313353802</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>421</v>
+      </c>
+      <c r="B84" t="s">
+        <v>4</v>
+      </c>
+      <c r="C84" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84">
+        <v>2.5744381145883901</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>422</v>
+      </c>
+      <c r="B85" t="s">
+        <v>4</v>
+      </c>
+      <c r="C85" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85">
+        <v>2.6562799514100099</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>431</v>
+      </c>
+      <c r="B86" t="s">
+        <v>4</v>
+      </c>
+      <c r="C86" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86">
+        <v>2.3741087446593299</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>511</v>
+      </c>
+      <c r="B87" t="s">
+        <v>4</v>
+      </c>
+      <c r="C87" t="s">
+        <v>5</v>
+      </c>
+      <c r="D87">
+        <v>1.4745695080758301</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>512</v>
+      </c>
+      <c r="B88" t="s">
+        <v>4</v>
+      </c>
+      <c r="C88" t="s">
+        <v>5</v>
+      </c>
+      <c r="D88">
+        <v>1.5485512191298001</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>513</v>
+      </c>
+      <c r="B89" t="s">
+        <v>4</v>
+      </c>
+      <c r="C89" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89">
+        <v>1.8418373676937201</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>514</v>
+      </c>
+      <c r="B90" t="s">
+        <v>4</v>
+      </c>
+      <c r="C90" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90">
+        <v>1.50871874261498</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>515</v>
+      </c>
+      <c r="B91" t="s">
+        <v>4</v>
+      </c>
+      <c r="C91" t="s">
+        <v>5</v>
+      </c>
+      <c r="D91">
+        <v>1.8949168215948</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>521</v>
+      </c>
+      <c r="B92" t="s">
+        <v>4</v>
+      </c>
+      <c r="C92" t="s">
+        <v>5</v>
+      </c>
+      <c r="D92">
+        <v>3.08817045507947</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>611</v>
+      </c>
+      <c r="B93" t="s">
+        <v>4</v>
+      </c>
+      <c r="C93" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93">
+        <v>1.5307039105493201</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>612</v>
+      </c>
+      <c r="B94" t="s">
+        <v>4</v>
+      </c>
+      <c r="C94" t="s">
+        <v>5</v>
+      </c>
+      <c r="D94">
+        <v>1.52189818341814</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>621</v>
+      </c>
+      <c r="B95" t="s">
+        <v>4</v>
+      </c>
+      <c r="C95" t="s">
+        <v>5</v>
+      </c>
+      <c r="D95">
+        <v>1.79280375772333</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>622</v>
+      </c>
+      <c r="B96" t="s">
+        <v>4</v>
+      </c>
+      <c r="C96" t="s">
+        <v>5</v>
+      </c>
+      <c r="D96">
+        <v>1.481056391489</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>711</v>
+      </c>
+      <c r="B97" t="s">
+        <v>4</v>
+      </c>
+      <c r="C97" t="s">
+        <v>5</v>
+      </c>
+      <c r="D97">
+        <v>1.6315971767625801</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>731</v>
+      </c>
+      <c r="B98" t="s">
+        <v>4</v>
+      </c>
+      <c r="C98" t="s">
+        <v>5</v>
+      </c>
+      <c r="D98">
+        <v>1.7261495856826099</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>811</v>
+      </c>
+      <c r="B99" t="s">
+        <v>4</v>
+      </c>
+      <c r="C99" t="s">
+        <v>5</v>
+      </c>
+      <c r="D99">
+        <v>1.2312786581750499</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>812</v>
+      </c>
+      <c r="B100" t="s">
+        <v>4</v>
+      </c>
+      <c r="C100" t="s">
+        <v>5</v>
+      </c>
+      <c r="D100">
+        <v>1.5776847726235901</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>813</v>
+      </c>
+      <c r="B101" t="s">
+        <v>4</v>
+      </c>
+      <c r="C101" t="s">
+        <v>5</v>
+      </c>
+      <c r="D101">
+        <v>2.0510694773218101</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>814</v>
+      </c>
+      <c r="B102" t="s">
+        <v>4</v>
+      </c>
+      <c r="C102" t="s">
+        <v>5</v>
+      </c>
+      <c r="D102">
+        <v>2.0951399255445899</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>821</v>
+      </c>
+      <c r="B103" t="s">
+        <v>4</v>
+      </c>
+      <c r="C103" t="s">
+        <v>5</v>
+      </c>
+      <c r="D103">
+        <v>1.5910973357649301</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>831</v>
+      </c>
+      <c r="B104" t="s">
+        <v>4</v>
+      </c>
+      <c r="C104" t="s">
+        <v>5</v>
+      </c>
+      <c r="D104">
+        <v>2.15714063175017</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>911</v>
+      </c>
+      <c r="B105" t="s">
+        <v>4</v>
+      </c>
+      <c r="C105" t="s">
+        <v>5</v>
+      </c>
+      <c r="D105">
+        <v>1.97407930138169</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>912</v>
+      </c>
+      <c r="B106" t="s">
+        <v>4</v>
+      </c>
+      <c r="C106" t="s">
+        <v>5</v>
+      </c>
+      <c r="D106">
+        <v>3.08923614825191</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>913</v>
+      </c>
+      <c r="B107" t="s">
+        <v>4</v>
+      </c>
+      <c r="C107" t="s">
+        <v>5</v>
+      </c>
+      <c r="D107">
+        <v>2.77775592840216</v>
       </c>
     </row>
   </sheetData>
